--- a/NOSOTROS/Angel/exposicion/PPP.xlsx
+++ b/NOSOTROS/Angel/exposicion/PPP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\OneDrive\Desktop\ANGEL CARRILLO\13-08-2026\ADSO_SENA\PROYECTO_ADSO_KJGA\NOSOTROS\Angel\exposicion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A721487-CB2D-4983-8282-BAA4BD9892D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47548AE-6D35-4D93-86EE-7A655BCBFC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10890" windowHeight="6900" activeTab="3" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -3006,7 +3006,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3128,12 +3128,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -3252,7 +3246,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3344,27 +3338,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3377,7 +3350,7 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3389,28 +3362,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
@@ -3418,6 +3382,45 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -3790,31 +3793,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -3835,16 +3838,16 @@
       <c r="F2" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="34" t="s">
         <v>305</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>648</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="34" t="s">
         <v>280</v>
       </c>
       <c r="K2" s="20" t="s">
@@ -6027,7 +6030,7 @@
       <c r="C33" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="D33" s="42" t="s">
+      <c r="D33" s="35" t="s">
         <v>929</v>
       </c>
       <c r="E33" s="6" t="s">
@@ -6057,7 +6060,7 @@
       <c r="M33" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="N33" s="43">
+      <c r="N33" s="36">
         <v>46277.427083333336</v>
       </c>
       <c r="O33" s="2" t="s">
@@ -6098,7 +6101,7 @@
       <c r="C34" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="D34" s="42" t="s">
+      <c r="D34" s="35" t="s">
         <v>930</v>
       </c>
       <c r="E34" s="6" t="s">
@@ -6128,7 +6131,7 @@
       <c r="M34" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="N34" s="43">
+      <c r="N34" s="36">
         <v>46277.597222222219</v>
       </c>
       <c r="O34" s="2" t="s">
@@ -6169,7 +6172,7 @@
       <c r="C35" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="35" t="s">
         <v>931</v>
       </c>
       <c r="E35" s="6" t="s">
@@ -6199,7 +6202,7 @@
       <c r="M35" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="N35" s="43">
+      <c r="N35" s="36">
         <v>46278.40625</v>
       </c>
       <c r="O35" s="2" t="s">
@@ -6231,40 +6234,40 @@
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="38"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="J39" s="38"/>
+      <c r="A39" s="31"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="J39" s="31"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="39"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="39"/>
-      <c r="J40" s="39"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="32"/>
+      <c r="J40" s="32"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="39"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="39"/>
-      <c r="J41" s="39"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="32"/>
+      <c r="J41" s="32"/>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="39"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="39"/>
-      <c r="J42" s="39"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="32"/>
+      <c r="J42" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6409,22 +6412,22 @@
       <c r="U2" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="V2" s="46" t="s">
+      <c r="V2" s="39" t="s">
         <v>632</v>
       </c>
-      <c r="W2" s="46" t="s">
+      <c r="W2" s="39" t="s">
         <v>633</v>
       </c>
-      <c r="X2" s="46" t="s">
+      <c r="X2" s="39" t="s">
         <v>634</v>
       </c>
-      <c r="Y2" s="46" t="s">
+      <c r="Y2" s="39" t="s">
         <v>428</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="Z2" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="AA2" s="46" t="s">
+      <c r="AA2" s="39" t="s">
         <v>912</v>
       </c>
     </row>
@@ -6480,7 +6483,7 @@
       <c r="Q3" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="R3" s="44">
+      <c r="R3" s="37">
         <v>46270.604166666664</v>
       </c>
       <c r="S3" s="6" t="s">
@@ -6563,7 +6566,7 @@
       <c r="Q4" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="R4" s="44">
+      <c r="R4" s="37">
         <v>46272.427083333336</v>
       </c>
       <c r="S4" s="6" t="s">
@@ -6646,7 +6649,7 @@
       <c r="Q5" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="37">
         <v>46267.697916666664</v>
       </c>
       <c r="S5" s="6" t="s">
@@ -6729,7 +6732,7 @@
       <c r="Q6" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="R6" s="44">
+      <c r="R6" s="37">
         <v>46266.805555555555</v>
       </c>
       <c r="S6" s="6" t="s">
@@ -6812,7 +6815,7 @@
       <c r="Q7" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="R7" s="44">
+      <c r="R7" s="37">
         <v>46271.479166666664</v>
       </c>
       <c r="S7" s="6" t="s">
@@ -6895,7 +6898,7 @@
       <c r="Q8" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="R8" s="44">
+      <c r="R8" s="37">
         <v>46269.361111111109</v>
       </c>
       <c r="S8" s="6" t="s">
@@ -6978,7 +6981,7 @@
       <c r="Q9" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="R9" s="44">
+      <c r="R9" s="37">
         <v>46268.715277777781</v>
       </c>
       <c r="S9" s="6" t="s">
@@ -7061,7 +7064,7 @@
       <c r="Q10" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="R10" s="44">
+      <c r="R10" s="37">
         <v>46273.392361111109</v>
       </c>
       <c r="S10" s="6" t="s">
@@ -7144,7 +7147,7 @@
       <c r="Q11" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="R11" s="44">
+      <c r="R11" s="37">
         <v>46263.576388888891</v>
       </c>
       <c r="S11" s="6" t="s">
@@ -7227,7 +7230,7 @@
       <c r="Q12" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="R12" s="44">
+      <c r="R12" s="37">
         <v>46265.753472222219</v>
       </c>
       <c r="S12" s="6" t="s">
@@ -7274,7 +7277,7 @@
       <c r="E13" s="6">
         <v>1002001001</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="6">
@@ -7304,13 +7307,13 @@
       <c r="O13" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="P13" s="45" t="s">
+      <c r="P13" s="38" t="s">
         <v>263</v>
       </c>
       <c r="Q13" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="R13" s="44">
+      <c r="R13" s="37">
         <v>46266.375</v>
       </c>
       <c r="S13" s="6" t="s">
@@ -7357,7 +7360,7 @@
       <c r="E14" s="6">
         <v>1002001001</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="38" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="6">
@@ -7387,16 +7390,16 @@
       <c r="O14" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P14" s="45" t="s">
+      <c r="P14" s="38" t="s">
         <v>266</v>
       </c>
       <c r="Q14" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="R14" s="44">
+      <c r="R14" s="37">
         <v>46280.375</v>
       </c>
-      <c r="S14" s="44">
+      <c r="S14" s="37">
         <v>46280.541666666664</v>
       </c>
       <c r="T14" s="7" t="s">
@@ -7440,7 +7443,7 @@
       <c r="E15" s="6">
         <v>1002001003</v>
       </c>
-      <c r="F15" s="45" t="s">
+      <c r="F15" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G15" s="6">
@@ -7470,16 +7473,16 @@
       <c r="O15" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P15" s="45" t="s">
+      <c r="P15" s="38" t="s">
         <v>268</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="R15" s="44">
+      <c r="R15" s="37">
         <v>46244.4375</v>
       </c>
-      <c r="S15" s="44">
+      <c r="S15" s="37">
         <v>46270.680555555555</v>
       </c>
       <c r="T15" s="7" t="s">
@@ -7523,7 +7526,7 @@
       <c r="E16" s="6">
         <v>1002001003</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G16" s="6">
@@ -7553,16 +7556,16 @@
       <c r="O16" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P16" s="45" t="s">
+      <c r="P16" s="38" t="s">
         <v>270</v>
       </c>
       <c r="Q16" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="R16" s="44">
+      <c r="R16" s="37">
         <v>46254.416666666664</v>
       </c>
-      <c r="S16" s="44">
+      <c r="S16" s="37">
         <v>46254.583333333336</v>
       </c>
       <c r="T16" s="7" t="s">
@@ -7606,7 +7609,7 @@
       <c r="E17" s="6">
         <v>1002001005</v>
       </c>
-      <c r="F17" s="45" t="s">
+      <c r="F17" s="38" t="s">
         <v>165</v>
       </c>
       <c r="G17" s="6">
@@ -7636,13 +7639,13 @@
       <c r="O17" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P17" s="45" t="s">
+      <c r="P17" s="38" t="s">
         <v>272</v>
       </c>
       <c r="Q17" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="R17" s="44">
+      <c r="R17" s="37">
         <v>46267.46875</v>
       </c>
       <c r="S17" s="7" t="s">
@@ -7689,7 +7692,7 @@
       <c r="E18" s="6">
         <v>1002001005</v>
       </c>
-      <c r="F18" s="45" t="s">
+      <c r="F18" s="38" t="s">
         <v>165</v>
       </c>
       <c r="G18" s="6">
@@ -7719,16 +7722,16 @@
       <c r="O18" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P18" s="45" t="s">
+      <c r="P18" s="38" t="s">
         <v>273</v>
       </c>
       <c r="Q18" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="R18" s="44">
+      <c r="R18" s="37">
         <v>46275.333333333336</v>
       </c>
-      <c r="S18" s="44">
+      <c r="S18" s="37">
         <v>46275.5</v>
       </c>
       <c r="T18" s="7" t="s">
@@ -7772,7 +7775,7 @@
       <c r="E19" s="6">
         <v>1002001007</v>
       </c>
-      <c r="F19" s="45" t="s">
+      <c r="F19" s="38" t="s">
         <v>32</v>
       </c>
       <c r="G19" s="6">
@@ -7802,13 +7805,13 @@
       <c r="O19" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P19" s="45" t="s">
+      <c r="P19" s="38" t="s">
         <v>275</v>
       </c>
       <c r="Q19" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="R19" s="44">
+      <c r="R19" s="37">
         <v>46268.597222222219</v>
       </c>
       <c r="S19" s="7" t="s">
@@ -7855,7 +7858,7 @@
       <c r="E20" s="6">
         <v>1002001007</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F20" s="38" t="s">
         <v>32</v>
       </c>
       <c r="G20" s="6">
@@ -7885,16 +7888,16 @@
       <c r="O20" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P20" s="45" t="s">
+      <c r="P20" s="38" t="s">
         <v>276</v>
       </c>
       <c r="Q20" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="R20" s="44">
+      <c r="R20" s="37">
         <v>46283.458333333336</v>
       </c>
-      <c r="S20" s="44">
+      <c r="S20" s="37">
         <v>46283.625</v>
       </c>
       <c r="T20" s="7" t="s">
@@ -7938,7 +7941,7 @@
       <c r="E21" s="6">
         <v>1002001009</v>
       </c>
-      <c r="F21" s="45" t="s">
+      <c r="F21" s="38" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="6">
@@ -7968,16 +7971,16 @@
       <c r="O21" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P21" s="45" t="s">
+      <c r="P21" s="38" t="s">
         <v>277</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="R21" s="44">
+      <c r="R21" s="37">
         <v>46259.395833333336</v>
       </c>
-      <c r="S21" s="44">
+      <c r="S21" s="37">
         <v>46273.65625</v>
       </c>
       <c r="T21" s="7" t="s">
@@ -8021,7 +8024,7 @@
       <c r="E22" s="6">
         <v>1002001009</v>
       </c>
-      <c r="F22" s="45" t="s">
+      <c r="F22" s="38" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="6">
@@ -8051,16 +8054,16 @@
       <c r="O22" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P22" s="45" t="s">
+      <c r="P22" s="38" t="s">
         <v>278</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="R22" s="44">
+      <c r="R22" s="37">
         <v>46259.375</v>
       </c>
-      <c r="S22" s="44">
+      <c r="S22" s="37">
         <v>46259.541666666664</v>
       </c>
       <c r="T22" s="7" t="s">
@@ -8104,7 +8107,7 @@
       <c r="E23" s="6">
         <v>1003001001</v>
       </c>
-      <c r="F23" s="45" t="s">
+      <c r="F23" s="38" t="s">
         <v>141</v>
       </c>
       <c r="G23" s="6">
@@ -8134,13 +8137,13 @@
       <c r="O23" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="P23" s="45" t="s">
+      <c r="P23" s="38" t="s">
         <v>263</v>
       </c>
       <c r="Q23" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="R23" s="44">
+      <c r="R23" s="37">
         <v>46266.375</v>
       </c>
       <c r="S23" s="7" t="s">
@@ -8187,7 +8190,7 @@
       <c r="E24" s="6">
         <v>1003001002</v>
       </c>
-      <c r="F24" s="45" t="s">
+      <c r="F24" s="38" t="s">
         <v>142</v>
       </c>
       <c r="G24" s="6">
@@ -8217,16 +8220,16 @@
       <c r="O24" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P24" s="45" t="s">
+      <c r="P24" s="38" t="s">
         <v>266</v>
       </c>
       <c r="Q24" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="R24" s="44">
+      <c r="R24" s="37">
         <v>46280.375</v>
       </c>
-      <c r="S24" s="44">
+      <c r="S24" s="37">
         <v>46280.541666666664</v>
       </c>
       <c r="T24" s="7" t="s">
@@ -8270,7 +8273,7 @@
       <c r="E25" s="6">
         <v>1003001003</v>
       </c>
-      <c r="F25" s="45" t="s">
+      <c r="F25" s="38" t="s">
         <v>143</v>
       </c>
       <c r="G25" s="6">
@@ -8300,16 +8303,16 @@
       <c r="O25" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P25" s="45" t="s">
+      <c r="P25" s="38" t="s">
         <v>268</v>
       </c>
       <c r="Q25" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="R25" s="44">
+      <c r="R25" s="37">
         <v>46244.4375</v>
       </c>
-      <c r="S25" s="44">
+      <c r="S25" s="37">
         <v>46270.680555555555</v>
       </c>
       <c r="T25" s="7" t="s">
@@ -8353,7 +8356,7 @@
       <c r="E26" s="6">
         <v>1003001004</v>
       </c>
-      <c r="F26" s="45" t="s">
+      <c r="F26" s="38" t="s">
         <v>144</v>
       </c>
       <c r="G26" s="6">
@@ -8383,16 +8386,16 @@
       <c r="O26" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P26" s="45" t="s">
+      <c r="P26" s="38" t="s">
         <v>270</v>
       </c>
       <c r="Q26" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="R26" s="44">
+      <c r="R26" s="37">
         <v>46254.416666666664</v>
       </c>
-      <c r="S26" s="44">
+      <c r="S26" s="37">
         <v>46254.583333333336</v>
       </c>
       <c r="T26" s="7" t="s">
@@ -8436,7 +8439,7 @@
       <c r="E27" s="6">
         <v>1003001005</v>
       </c>
-      <c r="F27" s="45" t="s">
+      <c r="F27" s="38" t="s">
         <v>145</v>
       </c>
       <c r="G27" s="6">
@@ -8466,13 +8469,13 @@
       <c r="O27" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P27" s="45" t="s">
+      <c r="P27" s="38" t="s">
         <v>272</v>
       </c>
       <c r="Q27" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="R27" s="44">
+      <c r="R27" s="37">
         <v>46267.46875</v>
       </c>
       <c r="S27" s="7" t="s">
@@ -8519,7 +8522,7 @@
       <c r="E28" s="6">
         <v>1003001006</v>
       </c>
-      <c r="F28" s="45" t="s">
+      <c r="F28" s="38" t="s">
         <v>146</v>
       </c>
       <c r="G28" s="6">
@@ -8549,16 +8552,16 @@
       <c r="O28" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P28" s="45" t="s">
+      <c r="P28" s="38" t="s">
         <v>273</v>
       </c>
       <c r="Q28" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="R28" s="44">
+      <c r="R28" s="37">
         <v>46275.333333333336</v>
       </c>
-      <c r="S28" s="44">
+      <c r="S28" s="37">
         <v>46275.5</v>
       </c>
       <c r="T28" s="7" t="s">
@@ -8602,7 +8605,7 @@
       <c r="E29" s="6">
         <v>1003001007</v>
       </c>
-      <c r="F29" s="45" t="s">
+      <c r="F29" s="38" t="s">
         <v>147</v>
       </c>
       <c r="G29" s="6">
@@ -8632,13 +8635,13 @@
       <c r="O29" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P29" s="45" t="s">
+      <c r="P29" s="38" t="s">
         <v>275</v>
       </c>
       <c r="Q29" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="R29" s="44">
+      <c r="R29" s="37">
         <v>46268.597222222219</v>
       </c>
       <c r="S29" s="7" t="s">
@@ -8685,7 +8688,7 @@
       <c r="E30" s="6">
         <v>1003001008</v>
       </c>
-      <c r="F30" s="45" t="s">
+      <c r="F30" s="38" t="s">
         <v>148</v>
       </c>
       <c r="G30" s="6">
@@ -8715,16 +8718,16 @@
       <c r="O30" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P30" s="45" t="s">
+      <c r="P30" s="38" t="s">
         <v>276</v>
       </c>
       <c r="Q30" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="R30" s="44">
+      <c r="R30" s="37">
         <v>46283.458333333336</v>
       </c>
-      <c r="S30" s="44">
+      <c r="S30" s="37">
         <v>46283.625</v>
       </c>
       <c r="T30" s="7" t="s">
@@ -8768,7 +8771,7 @@
       <c r="E31" s="6">
         <v>1003001009</v>
       </c>
-      <c r="F31" s="45" t="s">
+      <c r="F31" s="38" t="s">
         <v>149</v>
       </c>
       <c r="G31" s="6">
@@ -8798,16 +8801,16 @@
       <c r="O31" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P31" s="45" t="s">
+      <c r="P31" s="38" t="s">
         <v>277</v>
       </c>
       <c r="Q31" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="R31" s="44">
+      <c r="R31" s="37">
         <v>46259.395833333336</v>
       </c>
-      <c r="S31" s="44">
+      <c r="S31" s="37">
         <v>46273.65625</v>
       </c>
       <c r="T31" s="7" t="s">
@@ -8851,7 +8854,7 @@
       <c r="E32" s="6">
         <v>1003001010</v>
       </c>
-      <c r="F32" s="45" t="s">
+      <c r="F32" s="38" t="s">
         <v>150</v>
       </c>
       <c r="G32" s="6">
@@ -8881,16 +8884,16 @@
       <c r="O32" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P32" s="45" t="s">
+      <c r="P32" s="38" t="s">
         <v>278</v>
       </c>
       <c r="Q32" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="R32" s="44">
+      <c r="R32" s="37">
         <v>46259.375</v>
       </c>
-      <c r="S32" s="44">
+      <c r="S32" s="37">
         <v>46259.541666666664</v>
       </c>
       <c r="T32" s="7" t="s">
@@ -8922,22 +8925,22 @@
       <c r="A33" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="40" t="s">
         <v>960</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>961</v>
       </c>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="E33" s="48">
+      <c r="E33" s="40">
         <v>1012456789</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="F33" s="41" t="s">
         <v>923</v>
       </c>
-      <c r="G33" s="48">
+      <c r="G33" s="40">
         <v>3012456789</v>
       </c>
       <c r="H33" s="6" t="s">
@@ -8952,7 +8955,7 @@
       <c r="K33" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="L33" s="48" t="s">
+      <c r="L33" s="40" t="s">
         <v>296</v>
       </c>
       <c r="M33" s="6" t="s">
@@ -8964,16 +8967,16 @@
       <c r="O33" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="P33" s="45" t="s">
+      <c r="P33" s="38" t="s">
         <v>263</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>934</v>
       </c>
-      <c r="R33" s="48" t="s">
+      <c r="R33" s="40" t="s">
         <v>933</v>
       </c>
-      <c r="S33" s="48" t="s">
+      <c r="S33" s="40" t="s">
         <v>241</v>
       </c>
       <c r="T33" s="7" t="s">
@@ -8994,7 +8997,7 @@
       <c r="Y33" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="Z33" s="48" t="s">
+      <c r="Z33" s="40" t="s">
         <v>932</v>
       </c>
       <c r="AA33" s="6" t="s">
@@ -9005,22 +9008,22 @@
       <c r="A34" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="48" t="s">
+      <c r="B34" s="40" t="s">
         <v>962</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>964</v>
       </c>
-      <c r="D34" s="48" t="s">
+      <c r="D34" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="E34" s="48">
+      <c r="E34" s="40">
         <v>1023567890</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="F34" s="41" t="s">
         <v>924</v>
       </c>
-      <c r="G34" s="48">
+      <c r="G34" s="40">
         <v>3023567890</v>
       </c>
       <c r="H34" s="6" t="s">
@@ -9035,7 +9038,7 @@
       <c r="K34" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="L34" s="48" t="s">
+      <c r="L34" s="40" t="s">
         <v>298</v>
       </c>
       <c r="M34" s="6" t="s">
@@ -9047,16 +9050,16 @@
       <c r="O34" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P34" s="45" t="s">
+      <c r="P34" s="38" t="s">
         <v>272</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>979</v>
       </c>
-      <c r="R34" s="48" t="s">
+      <c r="R34" s="40" t="s">
         <v>936</v>
       </c>
-      <c r="S34" s="48" t="s">
+      <c r="S34" s="40" t="s">
         <v>940</v>
       </c>
       <c r="T34" s="7" t="s">
@@ -9077,7 +9080,7 @@
       <c r="Y34" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="Z34" s="48" t="s">
+      <c r="Z34" s="40" t="s">
         <v>935</v>
       </c>
       <c r="AA34" s="6" t="s">
@@ -9088,22 +9091,22 @@
       <c r="A35" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="48" t="s">
+      <c r="B35" s="40" t="s">
         <v>963</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="E35" s="48">
+      <c r="E35" s="40">
         <v>1034678901</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="41" t="s">
         <v>925</v>
       </c>
-      <c r="G35" s="48">
+      <c r="G35" s="40">
         <v>3034678901</v>
       </c>
       <c r="H35" s="6" t="s">
@@ -9118,7 +9121,7 @@
       <c r="K35" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="L35" s="48" t="s">
+      <c r="L35" s="40" t="s">
         <v>299</v>
       </c>
       <c r="M35" s="6" t="s">
@@ -9130,16 +9133,16 @@
       <c r="O35" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="P35" s="45" t="s">
+      <c r="P35" s="38" t="s">
         <v>275</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="R35" s="48" t="s">
+      <c r="R35" s="40" t="s">
         <v>938</v>
       </c>
-      <c r="S35" s="48" t="s">
+      <c r="S35" s="40" t="s">
         <v>941</v>
       </c>
       <c r="T35" s="7" t="s">
@@ -9160,7 +9163,7 @@
       <c r="Y35" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="Z35" s="48" t="s">
+      <c r="Z35" s="40" t="s">
         <v>937</v>
       </c>
       <c r="AA35" s="6" t="s">
@@ -9253,40 +9256,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="50"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="42"/>
       <c r="K1"/>
       <c r="L1"/>
       <c r="M1"/>
       <c r="N1"/>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="AC1" s="32" t="s">
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="AC1" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="AD1" s="32"/>
-      <c r="AF1" s="32" t="s">
+      <c r="AD1" s="52"/>
+      <c r="AF1" s="52" t="s">
         <v>393</v>
       </c>
-      <c r="AG1" s="32"/>
-      <c r="AI1" s="32" t="s">
+      <c r="AG1" s="52"/>
+      <c r="AI1" s="52" t="s">
         <v>536</v>
       </c>
-      <c r="AJ1" s="32"/>
+      <c r="AJ1" s="52"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -9310,7 +9313,7 @@
       <c r="G2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="50"/>
+      <c r="H2" s="42"/>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -9371,7 +9374,7 @@
       <c r="F3" s="1">
         <v>3001001001</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="35" t="s">
         <v>3</v>
       </c>
       <c r="K3"/>
@@ -9434,7 +9437,7 @@
       <c r="F4" s="1">
         <v>3001001002</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="35" t="s">
         <v>5</v>
       </c>
       <c r="K4"/>
@@ -9497,7 +9500,7 @@
       <c r="F5" s="1">
         <v>3001001003</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="35" t="s">
         <v>6</v>
       </c>
       <c r="K5"/>
@@ -9554,7 +9557,7 @@
       <c r="F6" s="1">
         <v>3001001004</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="35" t="s">
         <v>154</v>
       </c>
       <c r="K6"/>
@@ -9585,10 +9588,10 @@
       <c r="AD6" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="AF6" s="32" t="s">
+      <c r="AF6" s="52" t="s">
         <v>413</v>
       </c>
-      <c r="AG6" s="32"/>
+      <c r="AG6" s="52"/>
       <c r="AI6" s="2" t="s">
         <v>542</v>
       </c>
@@ -9615,7 +9618,7 @@
       <c r="F7" s="1">
         <v>3001001005</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="G7" s="35" t="s">
         <v>8</v>
       </c>
       <c r="K7"/>
@@ -9678,7 +9681,7 @@
       <c r="F8" s="1">
         <v>3001001006</v>
       </c>
-      <c r="G8" s="42" t="s">
+      <c r="G8" s="35" t="s">
         <v>10</v>
       </c>
       <c r="K8"/>
@@ -9741,7 +9744,7 @@
       <c r="F9" s="1">
         <v>3001001007</v>
       </c>
-      <c r="G9" s="42" t="s">
+      <c r="G9" s="35" t="s">
         <v>11</v>
       </c>
       <c r="K9"/>
@@ -9804,7 +9807,7 @@
       <c r="F10" s="1">
         <v>3001001008</v>
       </c>
-      <c r="G10" s="42" t="s">
+      <c r="G10" s="35" t="s">
         <v>13</v>
       </c>
       <c r="K10"/>
@@ -9861,7 +9864,7 @@
       <c r="F11" s="1">
         <v>3001001009</v>
       </c>
-      <c r="G11" s="42" t="s">
+      <c r="G11" s="35" t="s">
         <v>15</v>
       </c>
       <c r="K11"/>
@@ -9892,10 +9895,10 @@
       <c r="AD11" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="AF11" s="32" t="s">
+      <c r="AF11" s="52" t="s">
         <v>414</v>
       </c>
-      <c r="AG11" s="32"/>
+      <c r="AG11" s="52"/>
       <c r="AI11" s="2" t="s">
         <v>547</v>
       </c>
@@ -9922,7 +9925,7 @@
       <c r="F12" s="1">
         <v>3001001010</v>
       </c>
-      <c r="G12" s="42" t="s">
+      <c r="G12" s="35" t="s">
         <v>17</v>
       </c>
       <c r="K12"/>
@@ -9970,7 +9973,7 @@
       <c r="A13" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="40" t="s">
         <v>960</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -9979,13 +9982,13 @@
       <c r="D13" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="40">
         <v>1012456789</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="40">
         <v>3012456789</v>
       </c>
-      <c r="G13" s="49" t="s">
+      <c r="G13" s="41" t="s">
         <v>923</v>
       </c>
       <c r="H13"/>
@@ -10010,7 +10013,7 @@
       <c r="A14" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="40" t="s">
         <v>962</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -10019,36 +10022,36 @@
       <c r="D14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="40">
         <v>1023567890</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="40">
         <v>3023567890</v>
       </c>
-      <c r="G14" s="49" t="s">
+      <c r="G14" s="41" t="s">
         <v>924</v>
       </c>
       <c r="H14"/>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="51" t="s">
         <v>386</v>
       </c>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="AC14" s="32" t="s">
+      <c r="L14" s="51"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="51"/>
+      <c r="S14" s="51"/>
+      <c r="T14" s="51"/>
+      <c r="U14" s="51"/>
+      <c r="V14" s="51"/>
+      <c r="W14" s="51"/>
+      <c r="X14" s="51"/>
+      <c r="AC14" s="52" t="s">
         <v>235</v>
       </c>
-      <c r="AD14" s="32"/>
+      <c r="AD14" s="52"/>
       <c r="AF14" s="2" t="s">
         <v>426</v>
       </c>
@@ -10066,7 +10069,7 @@
       <c r="A15" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="40" t="s">
         <v>963</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -10075,13 +10078,13 @@
       <c r="D15" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="40">
         <v>1034678901</v>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="40">
         <v>3034678901</v>
       </c>
-      <c r="G15" s="49" t="s">
+      <c r="G15" s="41" t="s">
         <v>925</v>
       </c>
       <c r="H15"/>
@@ -10189,10 +10192,10 @@
       <c r="AD16" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="AF16" s="32" t="s">
+      <c r="AF16" s="52" t="s">
         <v>415</v>
       </c>
-      <c r="AG16" s="32"/>
+      <c r="AG16" s="52"/>
       <c r="AI16" s="2" t="s">
         <v>552</v>
       </c>
@@ -10201,15 +10204,15 @@
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
       <c r="K17" s="2" t="s">
         <v>399</v>
       </c>
@@ -10584,10 +10587,10 @@
       <c r="AD21" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="AF21" s="32" t="s">
+      <c r="AF21" s="52" t="s">
         <v>431</v>
       </c>
-      <c r="AG21" s="32"/>
+      <c r="AG21" s="52"/>
       <c r="AI21" s="2" t="s">
         <v>557</v>
       </c>
@@ -10824,15 +10827,15 @@
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
       <c r="K25" s="2" t="s">
         <v>407</v>
       </c>
@@ -10951,24 +10954,24 @@
       <c r="G27" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="K27" s="33" t="s">
+      <c r="K27" s="51" t="s">
         <v>410</v>
       </c>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="33"/>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="33"/>
-      <c r="Z27" s="33"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="51"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="51"/>
+      <c r="S27" s="51"/>
+      <c r="T27" s="51"/>
+      <c r="U27" s="51"/>
+      <c r="V27" s="51"/>
+      <c r="W27" s="51"/>
+      <c r="X27" s="51"/>
+      <c r="Y27" s="51"/>
+      <c r="Z27" s="51"/>
       <c r="AC27" s="2" t="s">
         <v>350</v>
       </c>
@@ -11058,10 +11061,10 @@
       <c r="AD28" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="AF28" s="32" t="s">
+      <c r="AF28" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="AG28" s="32"/>
+      <c r="AG28" s="52"/>
       <c r="AI28" s="2" t="s">
         <v>564</v>
       </c>
@@ -11592,17 +11595,17 @@
       <c r="G35" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="N35" s="34" t="s">
+      <c r="N35" s="54" t="s">
         <v>636</v>
       </c>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="34"/>
-      <c r="V35" s="34"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="54"/>
+      <c r="V35" s="54"/>
       <c r="W35" s="26"/>
       <c r="X35" s="26"/>
       <c r="Y35" s="26"/>
@@ -11719,10 +11722,10 @@
       </c>
       <c r="X37" s="26"/>
       <c r="Y37" s="26"/>
-      <c r="AC37" s="51" t="s">
+      <c r="AC37" s="48" t="s">
         <v>970</v>
       </c>
-      <c r="AD37" s="51"/>
+      <c r="AD37" s="48"/>
       <c r="AI37" s="2" t="s">
         <v>573</v>
       </c>
@@ -11731,15 +11734,15 @@
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="C38" s="33" t="s">
+      <c r="C38" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
       <c r="N38" s="1" t="s">
         <v>640</v>
       </c>
@@ -11769,16 +11772,16 @@
       </c>
       <c r="X38" s="26"/>
       <c r="Y38" s="26"/>
-      <c r="AC38" s="52" t="s">
+      <c r="AC38" s="43" t="s">
         <v>971</v>
       </c>
-      <c r="AD38" s="52" t="s">
+      <c r="AD38" s="43" t="s">
         <v>981</v>
       </c>
-      <c r="AF38" s="32" t="s">
+      <c r="AF38" s="52" t="s">
         <v>631</v>
       </c>
-      <c r="AG38" s="32"/>
+      <c r="AG38" s="52"/>
       <c r="AI38" s="2" t="s">
         <v>574</v>
       </c>
@@ -12043,17 +12046,17 @@
       <c r="I43" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="N43" s="53" t="s">
+      <c r="N43" s="49" t="s">
         <v>982</v>
       </c>
-      <c r="O43" s="53"/>
-      <c r="P43" s="53"/>
-      <c r="Q43" s="53"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="53"/>
-      <c r="T43" s="53"/>
-      <c r="U43" s="53"/>
-      <c r="V43" s="53"/>
+      <c r="O43" s="49"/>
+      <c r="P43" s="49"/>
+      <c r="Q43" s="49"/>
+      <c r="R43" s="49"/>
+      <c r="S43" s="49"/>
+      <c r="T43" s="49"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="49"/>
       <c r="AI43" s="2" t="s">
         <v>579</v>
       </c>
@@ -12083,31 +12086,31 @@
       <c r="I44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="N44" s="54" t="s">
+      <c r="N44" s="44" t="s">
         <v>983</v>
       </c>
-      <c r="O44" s="55" t="s">
+      <c r="O44" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="P44" s="54" t="s">
+      <c r="P44" s="44" t="s">
         <v>411</v>
       </c>
-      <c r="Q44" s="54" t="s">
+      <c r="Q44" s="44" t="s">
         <v>638</v>
       </c>
-      <c r="R44" s="54" t="s">
+      <c r="R44" s="44" t="s">
         <v>971</v>
       </c>
-      <c r="S44" s="54" t="s">
+      <c r="S44" s="44" t="s">
         <v>376</v>
       </c>
-      <c r="T44" s="55" t="s">
+      <c r="T44" s="45" t="s">
         <v>645</v>
       </c>
-      <c r="U44" s="55" t="s">
+      <c r="U44" s="45" t="s">
         <v>646</v>
       </c>
-      <c r="V44" s="55" t="s">
+      <c r="V44" s="45" t="s">
         <v>647</v>
       </c>
       <c r="Z44"/>
@@ -12138,13 +12141,13 @@
       <c r="S45" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="T45" s="48" t="s">
+      <c r="T45" s="40" t="s">
         <v>932</v>
       </c>
-      <c r="U45" s="48" t="s">
+      <c r="U45" s="40" t="s">
         <v>933</v>
       </c>
-      <c r="V45" s="48" t="s">
+      <c r="V45" s="40" t="s">
         <v>241</v>
       </c>
       <c r="Z45"/>
@@ -12175,13 +12178,13 @@
       <c r="S46" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="T46" s="48" t="s">
+      <c r="T46" s="40" t="s">
         <v>935</v>
       </c>
-      <c r="U46" s="48" t="s">
+      <c r="U46" s="40" t="s">
         <v>936</v>
       </c>
-      <c r="V46" s="48" t="s">
+      <c r="V46" s="40" t="s">
         <v>940</v>
       </c>
       <c r="Z46"/>
@@ -12212,13 +12215,13 @@
       <c r="S47" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="T47" s="48" t="s">
+      <c r="T47" s="40" t="s">
         <v>937</v>
       </c>
-      <c r="U47" s="48" t="s">
+      <c r="U47" s="40" t="s">
         <v>938</v>
       </c>
-      <c r="V47" s="48" t="s">
+      <c r="V47" s="40" t="s">
         <v>941</v>
       </c>
       <c r="AI47" s="2" t="s">
@@ -12633,14 +12636,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AC37:AD37"/>
-    <mergeCell ref="N43:V43"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="C38:I38"/>
-    <mergeCell ref="P1:U1"/>
-    <mergeCell ref="AC14:AD14"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="AF38:AG38"/>
     <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="AF28:AG28"/>
@@ -12653,6 +12648,14 @@
     <mergeCell ref="AF16:AG16"/>
     <mergeCell ref="AF21:AG21"/>
     <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AC37:AD37"/>
+    <mergeCell ref="N43:V43"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="P1:U1"/>
+    <mergeCell ref="AC14:AD14"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -12716,9 +12719,9 @@
     <col min="14" max="14" width="10.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.7109375" style="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.140625" style="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.28515625" style="12" customWidth="1"/>
     <col min="20" max="20" width="41.28515625" style="12" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="17.85546875" style="12" customWidth="1"/>
     <col min="23" max="23" width="7.85546875" style="12" bestFit="1" customWidth="1"/>
@@ -12738,36 +12741,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
       <c r="L1"/>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="AC1" s="32" t="s">
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="AC1" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="AD1" s="32"/>
-      <c r="AF1" s="32" t="s">
+      <c r="AD1" s="52"/>
+      <c r="AF1" s="52" t="s">
         <v>393</v>
       </c>
-      <c r="AG1" s="32"/>
-      <c r="AI1" s="32" t="s">
+      <c r="AG1" s="52"/>
+      <c r="AI1" s="52" t="s">
         <v>536</v>
       </c>
-      <c r="AJ1" s="32"/>
+      <c r="AJ1" s="52"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -13045,10 +13048,10 @@
       <c r="AD6" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="AF6" s="32" t="s">
+      <c r="AF6" s="52" t="s">
         <v>413</v>
       </c>
-      <c r="AG6" s="32"/>
+      <c r="AG6" s="52"/>
       <c r="AI6" s="2" t="s">
         <v>542</v>
       </c>
@@ -13320,14 +13323,14 @@
       <c r="T11" s="2">
         <v>8192755945</v>
       </c>
-      <c r="AC11" s="32" t="s">
+      <c r="AC11" s="52" t="s">
         <v>235</v>
       </c>
-      <c r="AD11" s="32"/>
-      <c r="AF11" s="32" t="s">
+      <c r="AD11" s="52"/>
+      <c r="AF11" s="52" t="s">
         <v>414</v>
       </c>
-      <c r="AG11" s="32"/>
+      <c r="AG11" s="52"/>
       <c r="AI11" s="2" t="s">
         <v>547</v>
       </c>
@@ -13415,31 +13418,31 @@
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="K14" s="33" t="s">
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="K14" s="51" t="s">
         <v>386</v>
       </c>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="51"/>
+      <c r="S14" s="51"/>
+      <c r="T14" s="51"/>
+      <c r="U14" s="51"/>
+      <c r="V14" s="51"/>
+      <c r="W14" s="51"/>
+      <c r="X14" s="51"/>
       <c r="AC14" s="2" t="s">
         <v>340</v>
       </c>
@@ -13606,10 +13609,10 @@
       <c r="AD16" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AF16" s="32" t="s">
+      <c r="AF16" s="52" t="s">
         <v>415</v>
       </c>
-      <c r="AG16" s="32"/>
+      <c r="AG16" s="52"/>
       <c r="AI16" s="2" t="s">
         <v>552</v>
       </c>
@@ -13992,10 +13995,10 @@
       <c r="AD21" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="AF21" s="32" t="s">
+      <c r="AF21" s="52" t="s">
         <v>431</v>
       </c>
-      <c r="AG21" s="32"/>
+      <c r="AG21" s="52"/>
       <c r="AI21" s="2" t="s">
         <v>557</v>
       </c>
@@ -14004,15 +14007,15 @@
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
       <c r="K22" s="2" t="s">
         <v>404</v>
       </c>
@@ -14380,24 +14383,24 @@
       <c r="G27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K27" s="33" t="s">
+      <c r="K27" s="51" t="s">
         <v>410</v>
       </c>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="33"/>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="33"/>
-      <c r="Z27" s="33"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="51"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="51"/>
+      <c r="S27" s="51"/>
+      <c r="T27" s="51"/>
+      <c r="U27" s="51"/>
+      <c r="V27" s="51"/>
+      <c r="W27" s="51"/>
+      <c r="X27" s="51"/>
+      <c r="Y27" s="51"/>
+      <c r="Z27" s="51"/>
       <c r="AC27" s="2" t="s">
         <v>353</v>
       </c>
@@ -14487,10 +14490,10 @@
       <c r="AD28" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="AF28" s="32" t="s">
+      <c r="AF28" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="AG28" s="32"/>
+      <c r="AG28" s="52"/>
       <c r="AI28" s="2" t="s">
         <v>564</v>
       </c>
@@ -14968,26 +14971,26 @@
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="C35" s="33" t="s">
+      <c r="C35" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="N35" s="34" t="s">
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="N35" s="54" t="s">
         <v>636</v>
       </c>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="34"/>
-      <c r="V35" s="34"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="54"/>
+      <c r="V35" s="54"/>
       <c r="W35" s="26"/>
       <c r="X35" s="26"/>
       <c r="Y35" s="26"/>
@@ -15036,13 +15039,13 @@
         <v>376</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>644</v>
+        <v>286</v>
       </c>
       <c r="R36" s="9" t="s">
         <v>282</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>286</v>
+        <v>644</v>
       </c>
       <c r="T36" s="10" t="s">
         <v>645</v>
@@ -15099,14 +15102,14 @@
       <c r="P37" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="Q37" s="6" t="s">
-        <v>649</v>
+      <c r="Q37" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="R37" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="S37" s="7" t="s">
-        <v>242</v>
+      <c r="S37" s="6" t="s">
+        <v>649</v>
       </c>
       <c r="T37" s="1" t="s">
         <v>661</v>
@@ -15164,14 +15167,14 @@
       <c r="P38" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="Q38" s="6" t="s">
-        <v>650</v>
+      <c r="Q38" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="R38" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="S38" s="7" t="s">
-        <v>242</v>
+      <c r="S38" s="6" t="s">
+        <v>650</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>662</v>
@@ -15223,14 +15226,14 @@
       <c r="P39" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="Q39" s="6" t="s">
-        <v>651</v>
+      <c r="Q39" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="R39" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>242</v>
+      <c r="S39" s="6" t="s">
+        <v>651</v>
       </c>
       <c r="T39" s="1" t="s">
         <v>663</v>
@@ -15282,14 +15285,14 @@
       <c r="P40" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="Q40" s="6" t="s">
-        <v>652</v>
+      <c r="Q40" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="R40" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="S40" s="7" t="s">
-        <v>242</v>
+      <c r="S40" s="6" t="s">
+        <v>652</v>
       </c>
       <c r="T40" s="1" t="s">
         <v>664</v>
@@ -15300,10 +15303,10 @@
       <c r="V40" s="14">
         <v>46283.625</v>
       </c>
-      <c r="AF40" s="32" t="s">
+      <c r="AF40" s="52" t="s">
         <v>631</v>
       </c>
-      <c r="AG40" s="32"/>
+      <c r="AG40" s="52"/>
       <c r="AI40" s="2" t="s">
         <v>576</v>
       </c>
@@ -15342,14 +15345,14 @@
       <c r="P41" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="Q41" s="6" t="s">
-        <v>653</v>
+      <c r="Q41" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="R41" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="S41" s="7" t="s">
-        <v>242</v>
+      <c r="S41" s="6" t="s">
+        <v>653</v>
       </c>
       <c r="T41" s="1" t="s">
         <v>665</v>
@@ -15402,22 +15405,22 @@
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A44" s="53" t="s">
+      <c r="A44" s="55" t="s">
         <v>982</v>
       </c>
-      <c r="B44" s="53"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="53"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="53"/>
-      <c r="I44" s="53"/>
-      <c r="S44" s="37" t="s">
+      <c r="B44" s="55"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
+      <c r="S44" s="57" t="s">
         <v>234</v>
       </c>
-      <c r="T44" s="37"/>
-      <c r="U44" s="37"/>
+      <c r="T44" s="57"/>
+      <c r="U44" s="57"/>
       <c r="AI44" s="2" t="s">
         <v>580</v>
       </c>
@@ -15426,40 +15429,40 @@
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A45" s="54" t="s">
+      <c r="A45" s="19" t="s">
         <v>983</v>
       </c>
-      <c r="B45" s="55" t="s">
+      <c r="B45" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="54" t="s">
+      <c r="C45" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D45" s="19" t="s">
         <v>638</v>
       </c>
-      <c r="E45" s="54" t="s">
+      <c r="E45" s="19" t="s">
         <v>971</v>
       </c>
-      <c r="F45" s="54" t="s">
+      <c r="F45" s="19" t="s">
         <v>376</v>
       </c>
-      <c r="G45" s="55" t="s">
+      <c r="G45" s="56" t="s">
         <v>645</v>
       </c>
-      <c r="H45" s="55" t="s">
+      <c r="H45" s="56" t="s">
         <v>646</v>
       </c>
-      <c r="I45" s="55" t="s">
+      <c r="I45" s="56" t="s">
         <v>647</v>
       </c>
-      <c r="S45" s="20" t="s">
+      <c r="S45" s="58" t="s">
         <v>660</v>
       </c>
-      <c r="T45" s="20" t="s">
+      <c r="T45" s="58" t="s">
         <v>280</v>
       </c>
-      <c r="U45" s="20" t="s">
+      <c r="U45" s="58" t="s">
         <v>307</v>
       </c>
       <c r="AI45" s="2" t="s">
@@ -15488,13 +15491,13 @@
       <c r="F46" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="G46" s="48" t="s">
+      <c r="G46" s="40" t="s">
         <v>932</v>
       </c>
-      <c r="H46" s="48" t="s">
+      <c r="H46" s="40" t="s">
         <v>933</v>
       </c>
-      <c r="I46" s="48" t="s">
+      <c r="I46" s="40" t="s">
         <v>241</v>
       </c>
       <c r="S46" s="2" t="s">
@@ -15532,13 +15535,13 @@
       <c r="F47" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="G47" s="48" t="s">
+      <c r="G47" s="40" t="s">
         <v>935</v>
       </c>
-      <c r="H47" s="48" t="s">
+      <c r="H47" s="40" t="s">
         <v>936</v>
       </c>
-      <c r="I47" s="48" t="s">
+      <c r="I47" s="40" t="s">
         <v>940</v>
       </c>
       <c r="S47" s="2" t="s">
@@ -15576,13 +15579,13 @@
       <c r="F48" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="G48" s="48" t="s">
+      <c r="G48" s="40" t="s">
         <v>937</v>
       </c>
-      <c r="H48" s="48" t="s">
+      <c r="H48" s="40" t="s">
         <v>938</v>
       </c>
-      <c r="I48" s="48" t="s">
+      <c r="I48" s="40" t="s">
         <v>941</v>
       </c>
       <c r="S48" s="2" t="s">
@@ -17186,26 +17189,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AF21:AG21"/>
+    <mergeCell ref="K14:X14"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AC11:AD11"/>
+    <mergeCell ref="AF11:AG11"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="AF16:AG16"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="C35:I35"/>
     <mergeCell ref="K27:Z27"/>
     <mergeCell ref="AF28:AG28"/>
     <mergeCell ref="N35:V35"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="AF16:AG16"/>
-    <mergeCell ref="AF21:AG21"/>
-    <mergeCell ref="K14:X14"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AF6:AG6"/>
     <mergeCell ref="AF40:AG40"/>
     <mergeCell ref="S44:U44"/>
-    <mergeCell ref="AC11:AD11"/>
-    <mergeCell ref="AF11:AG11"/>
-    <mergeCell ref="O1:T1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>

--- a/NOSOTROS/Angel/exposicion/PPP.xlsx
+++ b/NOSOTROS/Angel/exposicion/PPP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\OneDrive\Desktop\ANGEL CARRILLO\13-08-2026\ADSO_SENA\PROYECTO_ADSO_KJGA\NOSOTROS\Angel\exposicion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47548AE-6D35-4D93-86EE-7A655BCBFC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B11AE97-FB10-4962-9D8F-05EDE5F911A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10890" windowHeight="6900" activeTab="3" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11760" activeTab="3" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3639" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3654" uniqueCount="988">
   <si>
     <t>Director</t>
   </si>
@@ -3000,6 +2989,9 @@
   </si>
   <si>
     <t>PA003</t>
+  </si>
+  <si>
+    <t>id_Cl</t>
   </si>
 </sst>
 </file>
@@ -3374,14 +3366,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3389,8 +3384,14 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3398,28 +3399,19 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3793,31 +3785,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -6318,35 +6310,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
@@ -9256,40 +9248,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
       <c r="H1" s="42"/>
       <c r="K1"/>
       <c r="L1"/>
       <c r="M1"/>
       <c r="N1"/>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="AC1" s="52" t="s">
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="AC1" s="49" t="s">
         <v>236</v>
       </c>
-      <c r="AD1" s="52"/>
-      <c r="AF1" s="52" t="s">
+      <c r="AD1" s="49"/>
+      <c r="AF1" s="49" t="s">
         <v>393</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AI1" s="52" t="s">
+      <c r="AG1" s="49"/>
+      <c r="AI1" s="49" t="s">
         <v>536</v>
       </c>
-      <c r="AJ1" s="52"/>
+      <c r="AJ1" s="49"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -9588,10 +9580,10 @@
       <c r="AD6" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="AF6" s="52" t="s">
+      <c r="AF6" s="49" t="s">
         <v>413</v>
       </c>
-      <c r="AG6" s="52"/>
+      <c r="AG6" s="49"/>
       <c r="AI6" s="2" t="s">
         <v>542</v>
       </c>
@@ -9895,10 +9887,10 @@
       <c r="AD11" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="AF11" s="52" t="s">
+      <c r="AF11" s="49" t="s">
         <v>414</v>
       </c>
-      <c r="AG11" s="52"/>
+      <c r="AG11" s="49"/>
       <c r="AI11" s="2" t="s">
         <v>547</v>
       </c>
@@ -10032,26 +10024,26 @@
         <v>924</v>
       </c>
       <c r="H14"/>
-      <c r="K14" s="51" t="s">
+      <c r="K14" s="50" t="s">
         <v>386</v>
       </c>
-      <c r="L14" s="51"/>
-      <c r="M14" s="51"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="51"/>
-      <c r="S14" s="51"/>
-      <c r="T14" s="51"/>
-      <c r="U14" s="51"/>
-      <c r="V14" s="51"/>
-      <c r="W14" s="51"/>
-      <c r="X14" s="51"/>
-      <c r="AC14" s="52" t="s">
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="50"/>
+      <c r="T14" s="50"/>
+      <c r="U14" s="50"/>
+      <c r="V14" s="50"/>
+      <c r="W14" s="50"/>
+      <c r="X14" s="50"/>
+      <c r="AC14" s="49" t="s">
         <v>235</v>
       </c>
-      <c r="AD14" s="52"/>
+      <c r="AD14" s="49"/>
       <c r="AF14" s="2" t="s">
         <v>426</v>
       </c>
@@ -10192,10 +10184,10 @@
       <c r="AD16" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="AF16" s="52" t="s">
+      <c r="AF16" s="49" t="s">
         <v>415</v>
       </c>
-      <c r="AG16" s="52"/>
+      <c r="AG16" s="49"/>
       <c r="AI16" s="2" t="s">
         <v>552</v>
       </c>
@@ -10204,15 +10196,15 @@
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="53"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
       <c r="K17" s="2" t="s">
         <v>399</v>
       </c>
@@ -10587,10 +10579,10 @@
       <c r="AD21" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="AF21" s="52" t="s">
+      <c r="AF21" s="49" t="s">
         <v>431</v>
       </c>
-      <c r="AG21" s="52"/>
+      <c r="AG21" s="49"/>
       <c r="AI21" s="2" t="s">
         <v>557</v>
       </c>
@@ -10827,15 +10819,15 @@
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
       <c r="K25" s="2" t="s">
         <v>407</v>
       </c>
@@ -10954,24 +10946,24 @@
       <c r="G27" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="K27" s="51" t="s">
+      <c r="K27" s="50" t="s">
         <v>410</v>
       </c>
-      <c r="L27" s="51"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="51"/>
-      <c r="S27" s="51"/>
-      <c r="T27" s="51"/>
-      <c r="U27" s="51"/>
-      <c r="V27" s="51"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="51"/>
-      <c r="Y27" s="51"/>
-      <c r="Z27" s="51"/>
+      <c r="L27" s="50"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
+      <c r="W27" s="50"/>
+      <c r="X27" s="50"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="50"/>
       <c r="AC27" s="2" t="s">
         <v>350</v>
       </c>
@@ -11061,10 +11053,10 @@
       <c r="AD28" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="AF28" s="52" t="s">
+      <c r="AF28" s="49" t="s">
         <v>233</v>
       </c>
-      <c r="AG28" s="52"/>
+      <c r="AG28" s="49"/>
       <c r="AI28" s="2" t="s">
         <v>564</v>
       </c>
@@ -11121,11 +11113,11 @@
       <c r="S29" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="T29" s="14">
-        <v>46266.375</v>
-      </c>
-      <c r="U29" s="6" t="s">
-        <v>4</v>
+      <c r="T29" s="40" t="s">
+        <v>933</v>
+      </c>
+      <c r="U29" s="40" t="s">
+        <v>241</v>
       </c>
       <c r="V29" s="7" t="s">
         <v>242</v>
@@ -11299,11 +11291,11 @@
       <c r="S31" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="T31" s="14">
-        <v>46267.46875</v>
-      </c>
-      <c r="U31" s="6" t="s">
-        <v>4</v>
+      <c r="T31" s="40" t="s">
+        <v>936</v>
+      </c>
+      <c r="U31" s="40" t="s">
+        <v>940</v>
       </c>
       <c r="V31" s="7" t="s">
         <v>242</v>
@@ -11388,11 +11380,11 @@
       <c r="S32" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="T32" s="14">
-        <v>46268.597222222219</v>
-      </c>
-      <c r="U32" s="6" t="s">
-        <v>4</v>
+      <c r="T32" s="40" t="s">
+        <v>938</v>
+      </c>
+      <c r="U32" s="40" t="s">
+        <v>941</v>
       </c>
       <c r="V32" s="7" t="s">
         <v>242</v>
@@ -11595,17 +11587,17 @@
       <c r="G35" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="N35" s="54" t="s">
+      <c r="N35" s="51" t="s">
         <v>636</v>
       </c>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54"/>
-      <c r="Q35" s="54"/>
-      <c r="R35" s="54"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="54"/>
-      <c r="V35" s="54"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="51"/>
+      <c r="Q35" s="51"/>
+      <c r="R35" s="51"/>
+      <c r="S35" s="51"/>
+      <c r="T35" s="51"/>
+      <c r="U35" s="51"/>
+      <c r="V35" s="51"/>
       <c r="W35" s="26"/>
       <c r="X35" s="26"/>
       <c r="Y35" s="26"/>
@@ -11722,10 +11714,10 @@
       </c>
       <c r="X37" s="26"/>
       <c r="Y37" s="26"/>
-      <c r="AC37" s="48" t="s">
+      <c r="AC37" s="57" t="s">
         <v>970</v>
       </c>
-      <c r="AD37" s="48"/>
+      <c r="AD37" s="57"/>
       <c r="AI37" s="2" t="s">
         <v>573</v>
       </c>
@@ -11734,15 +11726,15 @@
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="C38" s="51" t="s">
+      <c r="C38" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="50"/>
       <c r="N38" s="1" t="s">
         <v>640</v>
       </c>
@@ -11772,16 +11764,16 @@
       </c>
       <c r="X38" s="26"/>
       <c r="Y38" s="26"/>
-      <c r="AC38" s="43" t="s">
+      <c r="AC38" s="58" t="s">
         <v>971</v>
       </c>
-      <c r="AD38" s="43" t="s">
+      <c r="AD38" s="58" t="s">
         <v>981</v>
       </c>
-      <c r="AF38" s="52" t="s">
+      <c r="AF38" s="49" t="s">
         <v>631</v>
       </c>
-      <c r="AG38" s="52"/>
+      <c r="AG38" s="49"/>
       <c r="AI38" s="2" t="s">
         <v>574</v>
       </c>
@@ -12046,17 +12038,17 @@
       <c r="I43" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="N43" s="49" t="s">
+      <c r="N43" s="52" t="s">
         <v>982</v>
       </c>
-      <c r="O43" s="49"/>
-      <c r="P43" s="49"/>
-      <c r="Q43" s="49"/>
-      <c r="R43" s="49"/>
-      <c r="S43" s="49"/>
-      <c r="T43" s="49"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="49"/>
+      <c r="O43" s="52"/>
+      <c r="P43" s="52"/>
+      <c r="Q43" s="52"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="52"/>
+      <c r="T43" s="52"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="52"/>
       <c r="AI43" s="2" t="s">
         <v>579</v>
       </c>
@@ -12086,31 +12078,31 @@
       <c r="I44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="N44" s="44" t="s">
+      <c r="N44" s="43" t="s">
         <v>983</v>
       </c>
-      <c r="O44" s="45" t="s">
+      <c r="O44" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="P44" s="44" t="s">
+      <c r="P44" s="43" t="s">
         <v>411</v>
       </c>
-      <c r="Q44" s="44" t="s">
+      <c r="Q44" s="43" t="s">
         <v>638</v>
       </c>
-      <c r="R44" s="44" t="s">
+      <c r="R44" s="43" t="s">
         <v>971</v>
       </c>
-      <c r="S44" s="44" t="s">
+      <c r="S44" s="43" t="s">
         <v>376</v>
       </c>
-      <c r="T44" s="45" t="s">
+      <c r="T44" s="44" t="s">
         <v>645</v>
       </c>
-      <c r="U44" s="45" t="s">
+      <c r="U44" s="44" t="s">
         <v>646</v>
       </c>
-      <c r="V44" s="45" t="s">
+      <c r="V44" s="44" t="s">
         <v>647</v>
       </c>
       <c r="Z44"/>
@@ -12636,6 +12628,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N43:V43"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="P1:U1"/>
+    <mergeCell ref="AC14:AD14"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="AF38:AG38"/>
     <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="AF28:AG28"/>
@@ -12649,13 +12648,6 @@
     <mergeCell ref="AF21:AG21"/>
     <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="AC37:AD37"/>
-    <mergeCell ref="N43:V43"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="C38:I38"/>
-    <mergeCell ref="P1:U1"/>
-    <mergeCell ref="AC14:AD14"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -12703,7 +12695,7 @@
   <dimension ref="A1:AJ165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="12" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" style="12" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" style="12" bestFit="1" customWidth="1"/>
@@ -12732,49 +12724,49 @@
     <col min="29" max="29" width="9.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="20" style="12" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="11.42578125" style="12"/>
-    <col min="32" max="32" width="9.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.7109375" style="12" customWidth="1"/>
+    <col min="33" max="33" width="10.7109375" style="12" customWidth="1"/>
     <col min="34" max="34" width="11.42578125" style="12"/>
-    <col min="35" max="35" width="7.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.140625" style="12" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="12.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11.42578125" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
       <c r="L1"/>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="AC1" s="52" t="s">
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="AC1" s="49" t="s">
         <v>236</v>
       </c>
-      <c r="AD1" s="52"/>
-      <c r="AF1" s="52" t="s">
+      <c r="AD1" s="49"/>
+      <c r="AF1" s="49" t="s">
         <v>393</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AI1" s="52" t="s">
+      <c r="AG1" s="49"/>
+      <c r="AI1" s="49" t="s">
         <v>536</v>
       </c>
-      <c r="AJ1" s="52"/>
+      <c r="AJ1" s="49"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>88</v>
+        <v>987</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>302</v>
@@ -13048,10 +13040,10 @@
       <c r="AD6" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="AF6" s="52" t="s">
+      <c r="AF6" s="49" t="s">
         <v>413</v>
       </c>
-      <c r="AG6" s="52"/>
+      <c r="AG6" s="49"/>
       <c r="AI6" s="2" t="s">
         <v>542</v>
       </c>
@@ -13323,14 +13315,14 @@
       <c r="T11" s="2">
         <v>8192755945</v>
       </c>
-      <c r="AC11" s="52" t="s">
+      <c r="AC11" s="49" t="s">
         <v>235</v>
       </c>
-      <c r="AD11" s="52"/>
-      <c r="AF11" s="52" t="s">
+      <c r="AD11" s="49"/>
+      <c r="AF11" s="49" t="s">
         <v>414</v>
       </c>
-      <c r="AG11" s="52"/>
+      <c r="AG11" s="49"/>
       <c r="AI11" s="2" t="s">
         <v>547</v>
       </c>
@@ -13418,31 +13410,31 @@
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="K14" s="51" t="s">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="K14" s="50" t="s">
         <v>386</v>
       </c>
-      <c r="L14" s="51"/>
-      <c r="M14" s="51"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="51"/>
-      <c r="S14" s="51"/>
-      <c r="T14" s="51"/>
-      <c r="U14" s="51"/>
-      <c r="V14" s="51"/>
-      <c r="W14" s="51"/>
-      <c r="X14" s="51"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="50"/>
+      <c r="T14" s="50"/>
+      <c r="U14" s="50"/>
+      <c r="V14" s="50"/>
+      <c r="W14" s="50"/>
+      <c r="X14" s="50"/>
       <c r="AC14" s="2" t="s">
         <v>340</v>
       </c>
@@ -13609,10 +13601,10 @@
       <c r="AD16" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AF16" s="52" t="s">
+      <c r="AF16" s="49" t="s">
         <v>415</v>
       </c>
-      <c r="AG16" s="52"/>
+      <c r="AG16" s="49"/>
       <c r="AI16" s="2" t="s">
         <v>552</v>
       </c>
@@ -13995,10 +13987,10 @@
       <c r="AD21" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="AF21" s="52" t="s">
+      <c r="AF21" s="49" t="s">
         <v>431</v>
       </c>
-      <c r="AG21" s="52"/>
+      <c r="AG21" s="49"/>
       <c r="AI21" s="2" t="s">
         <v>557</v>
       </c>
@@ -14007,15 +13999,15 @@
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
       <c r="K22" s="2" t="s">
         <v>404</v>
       </c>
@@ -14383,24 +14375,24 @@
       <c r="G27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K27" s="51" t="s">
+      <c r="K27" s="50" t="s">
         <v>410</v>
       </c>
-      <c r="L27" s="51"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="51"/>
-      <c r="S27" s="51"/>
-      <c r="T27" s="51"/>
-      <c r="U27" s="51"/>
-      <c r="V27" s="51"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="51"/>
-      <c r="Y27" s="51"/>
-      <c r="Z27" s="51"/>
+      <c r="L27" s="50"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
+      <c r="W27" s="50"/>
+      <c r="X27" s="50"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="50"/>
       <c r="AC27" s="2" t="s">
         <v>353</v>
       </c>
@@ -14490,10 +14482,10 @@
       <c r="AD28" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="AF28" s="52" t="s">
+      <c r="AF28" s="49" t="s">
         <v>233</v>
       </c>
-      <c r="AG28" s="52"/>
+      <c r="AG28" s="49"/>
       <c r="AI28" s="2" t="s">
         <v>564</v>
       </c>
@@ -14550,11 +14542,11 @@
       <c r="S29" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="T29" s="14">
-        <v>46266.375</v>
-      </c>
-      <c r="U29" s="6" t="s">
-        <v>4</v>
+      <c r="T29" s="40" t="s">
+        <v>933</v>
+      </c>
+      <c r="U29" s="40" t="s">
+        <v>241</v>
       </c>
       <c r="V29" s="7" t="s">
         <v>242</v>
@@ -14728,11 +14720,11 @@
       <c r="S31" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="T31" s="14">
-        <v>46267.46875</v>
-      </c>
-      <c r="U31" s="6" t="s">
-        <v>4</v>
+      <c r="T31" s="40" t="s">
+        <v>936</v>
+      </c>
+      <c r="U31" s="40" t="s">
+        <v>940</v>
       </c>
       <c r="V31" s="7" t="s">
         <v>242</v>
@@ -14817,11 +14809,11 @@
       <c r="S32" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="T32" s="14">
-        <v>46268.597222222219</v>
-      </c>
-      <c r="U32" s="6" t="s">
-        <v>4</v>
+      <c r="T32" s="40" t="s">
+        <v>938</v>
+      </c>
+      <c r="U32" s="40" t="s">
+        <v>941</v>
       </c>
       <c r="V32" s="7" t="s">
         <v>242</v>
@@ -14957,6 +14949,10 @@
       <c r="X34" s="25"/>
       <c r="Y34" s="25"/>
       <c r="Z34" s="25"/>
+      <c r="AC34" s="57" t="s">
+        <v>970</v>
+      </c>
+      <c r="AD34" s="57"/>
       <c r="AF34" s="2" t="s">
         <v>373</v>
       </c>
@@ -14971,29 +14967,35 @@
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="N35" s="54" t="s">
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="N35" s="51" t="s">
         <v>636</v>
       </c>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54"/>
-      <c r="Q35" s="54"/>
-      <c r="R35" s="54"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="54"/>
-      <c r="V35" s="54"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="51"/>
+      <c r="Q35" s="51"/>
+      <c r="R35" s="51"/>
+      <c r="S35" s="51"/>
+      <c r="T35" s="51"/>
+      <c r="U35" s="51"/>
+      <c r="V35" s="51"/>
       <c r="W35" s="26"/>
       <c r="X35" s="26"/>
       <c r="Y35" s="26"/>
+      <c r="AC35" s="58" t="s">
+        <v>971</v>
+      </c>
+      <c r="AD35" s="58" t="s">
+        <v>981</v>
+      </c>
       <c r="AF35" s="2" t="s">
         <v>374</v>
       </c>
@@ -15058,6 +15060,12 @@
       </c>
       <c r="X36" s="26"/>
       <c r="Y36" s="26"/>
+      <c r="AC36" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="AD36" s="2" t="s">
+        <v>972</v>
+      </c>
       <c r="AF36" s="2" t="s">
         <v>375</v>
       </c>
@@ -15123,6 +15131,12 @@
       <c r="W37" s="26"/>
       <c r="X37" s="26"/>
       <c r="Y37" s="26"/>
+      <c r="AC37" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="AD37" s="2" t="s">
+        <v>973</v>
+      </c>
       <c r="AF37" s="2" t="s">
         <v>897</v>
       </c>
@@ -15188,6 +15202,12 @@
       <c r="W38" s="26"/>
       <c r="X38" s="26"/>
       <c r="Y38" s="26"/>
+      <c r="AC38" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="AD38" s="2" t="s">
+        <v>974</v>
+      </c>
       <c r="AI38" s="2" t="s">
         <v>574</v>
       </c>
@@ -15303,10 +15323,10 @@
       <c r="V40" s="14">
         <v>46283.625</v>
       </c>
-      <c r="AF40" s="52" t="s">
+      <c r="AF40" s="49" t="s">
         <v>631</v>
       </c>
-      <c r="AG40" s="52"/>
+      <c r="AG40" s="49"/>
       <c r="AI40" s="2" t="s">
         <v>576</v>
       </c>
@@ -15416,11 +15436,11 @@
       <c r="G44" s="55"/>
       <c r="H44" s="55"/>
       <c r="I44" s="55"/>
-      <c r="S44" s="57" t="s">
+      <c r="S44" s="56" t="s">
         <v>234</v>
       </c>
-      <c r="T44" s="57"/>
-      <c r="U44" s="57"/>
+      <c r="T44" s="56"/>
+      <c r="U44" s="56"/>
       <c r="AI44" s="2" t="s">
         <v>580</v>
       </c>
@@ -15432,8 +15452,8 @@
       <c r="A45" s="19" t="s">
         <v>983</v>
       </c>
-      <c r="B45" s="56" t="s">
-        <v>88</v>
+      <c r="B45" s="45" t="s">
+        <v>987</v>
       </c>
       <c r="C45" s="19" t="s">
         <v>411</v>
@@ -15447,22 +15467,22 @@
       <c r="F45" s="19" t="s">
         <v>376</v>
       </c>
-      <c r="G45" s="56" t="s">
+      <c r="G45" s="45" t="s">
         <v>645</v>
       </c>
-      <c r="H45" s="56" t="s">
+      <c r="H45" s="45" t="s">
         <v>646</v>
       </c>
-      <c r="I45" s="56" t="s">
+      <c r="I45" s="45" t="s">
         <v>647</v>
       </c>
-      <c r="S45" s="58" t="s">
+      <c r="S45" s="46" t="s">
         <v>660</v>
       </c>
-      <c r="T45" s="58" t="s">
+      <c r="T45" s="46" t="s">
         <v>280</v>
       </c>
-      <c r="U45" s="58" t="s">
+      <c r="U45" s="46" t="s">
         <v>307</v>
       </c>
       <c r="AI45" s="2" t="s">
@@ -17188,7 +17208,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="K27:Z27"/>
+    <mergeCell ref="AF28:AG28"/>
+    <mergeCell ref="N35:V35"/>
+    <mergeCell ref="AF40:AG40"/>
+    <mergeCell ref="S44:U44"/>
+    <mergeCell ref="AC34:AD34"/>
     <mergeCell ref="AF21:AG21"/>
     <mergeCell ref="K14:X14"/>
     <mergeCell ref="A22:G22"/>
@@ -17202,13 +17230,6 @@
     <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="AF16:AG16"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="K27:Z27"/>
-    <mergeCell ref="AF28:AG28"/>
-    <mergeCell ref="N35:V35"/>
-    <mergeCell ref="AF40:AG40"/>
-    <mergeCell ref="S44:U44"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>

--- a/NOSOTROS/Angel/exposicion/PPP.xlsx
+++ b/NOSOTROS/Angel/exposicion/PPP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\OneDrive\Desktop\ANGEL CARRILLO\13-08-2026\ADSO_SENA\PROYECTO_ADSO_KJGA\NOSOTROS\Angel\exposicion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Documents\ADSO, 2006\PROYECTO_ADSO_KJGA\NOSOTROS\Angel\exposicion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B11AE97-FB10-4962-9D8F-05EDE5F911A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4456535B-9457-4ADF-AE24-C34C2CD42855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11760" activeTab="3" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D1012828-DDFC-47C0-86DB-3A2BD43233B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3654" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="989">
   <si>
     <t>Director</t>
   </si>
@@ -2992,6 +2995,9 @@
   </si>
   <si>
     <t>id_Cl</t>
+  </si>
+  <si>
+    <t>id_CL</t>
   </si>
 </sst>
 </file>
@@ -3202,7 +3208,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -3214,6 +3220,43 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -3238,7 +3281,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3378,6 +3421,9 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3393,6 +3439,9 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3402,16 +3451,19 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3785,31 +3837,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="48" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -6310,35 +6362,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
@@ -9248,40 +9300,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="42"/>
       <c r="K1"/>
       <c r="L1"/>
       <c r="M1"/>
       <c r="N1"/>
-      <c r="P1" s="50" t="s">
+      <c r="P1" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="AC1" s="49" t="s">
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="AC1" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="AD1" s="49"/>
-      <c r="AF1" s="49" t="s">
+      <c r="AD1" s="50"/>
+      <c r="AF1" s="50" t="s">
         <v>393</v>
       </c>
-      <c r="AG1" s="49"/>
-      <c r="AI1" s="49" t="s">
+      <c r="AG1" s="50"/>
+      <c r="AI1" s="50" t="s">
         <v>536</v>
       </c>
-      <c r="AJ1" s="49"/>
+      <c r="AJ1" s="50"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -9580,10 +9632,10 @@
       <c r="AD6" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="AF6" s="49" t="s">
+      <c r="AF6" s="50" t="s">
         <v>413</v>
       </c>
-      <c r="AG6" s="49"/>
+      <c r="AG6" s="50"/>
       <c r="AI6" s="2" t="s">
         <v>542</v>
       </c>
@@ -9887,10 +9939,10 @@
       <c r="AD11" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="AF11" s="49" t="s">
+      <c r="AF11" s="50" t="s">
         <v>414</v>
       </c>
-      <c r="AG11" s="49"/>
+      <c r="AG11" s="50"/>
       <c r="AI11" s="2" t="s">
         <v>547</v>
       </c>
@@ -10024,26 +10076,26 @@
         <v>924</v>
       </c>
       <c r="H14"/>
-      <c r="K14" s="50" t="s">
+      <c r="K14" s="51" t="s">
         <v>386</v>
       </c>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="50"/>
-      <c r="P14" s="50"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50"/>
-      <c r="S14" s="50"/>
-      <c r="T14" s="50"/>
-      <c r="U14" s="50"/>
-      <c r="V14" s="50"/>
-      <c r="W14" s="50"/>
-      <c r="X14" s="50"/>
-      <c r="AC14" s="49" t="s">
+      <c r="L14" s="51"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="51"/>
+      <c r="S14" s="51"/>
+      <c r="T14" s="51"/>
+      <c r="U14" s="51"/>
+      <c r="V14" s="51"/>
+      <c r="W14" s="51"/>
+      <c r="X14" s="51"/>
+      <c r="AC14" s="50" t="s">
         <v>235</v>
       </c>
-      <c r="AD14" s="49"/>
+      <c r="AD14" s="50"/>
       <c r="AF14" s="2" t="s">
         <v>426</v>
       </c>
@@ -10184,10 +10236,10 @@
       <c r="AD16" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="AF16" s="49" t="s">
+      <c r="AF16" s="50" t="s">
         <v>415</v>
       </c>
-      <c r="AG16" s="49"/>
+      <c r="AG16" s="50"/>
       <c r="AI16" s="2" t="s">
         <v>552</v>
       </c>
@@ -10196,15 +10248,15 @@
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
       <c r="K17" s="2" t="s">
         <v>399</v>
       </c>
@@ -10579,10 +10631,10 @@
       <c r="AD21" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="AF21" s="49" t="s">
+      <c r="AF21" s="50" t="s">
         <v>431</v>
       </c>
-      <c r="AG21" s="49"/>
+      <c r="AG21" s="50"/>
       <c r="AI21" s="2" t="s">
         <v>557</v>
       </c>
@@ -10819,15 +10871,15 @@
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
       <c r="K25" s="2" t="s">
         <v>407</v>
       </c>
@@ -10946,24 +10998,24 @@
       <c r="G27" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="K27" s="50" t="s">
+      <c r="K27" s="51" t="s">
         <v>410</v>
       </c>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="50"/>
-      <c r="W27" s="50"/>
-      <c r="X27" s="50"/>
-      <c r="Y27" s="50"/>
-      <c r="Z27" s="50"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="51"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="51"/>
+      <c r="S27" s="51"/>
+      <c r="T27" s="51"/>
+      <c r="U27" s="51"/>
+      <c r="V27" s="51"/>
+      <c r="W27" s="51"/>
+      <c r="X27" s="51"/>
+      <c r="Y27" s="51"/>
+      <c r="Z27" s="51"/>
       <c r="AC27" s="2" t="s">
         <v>350</v>
       </c>
@@ -11053,10 +11105,10 @@
       <c r="AD28" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="AG28" s="49"/>
+      <c r="AG28" s="50"/>
       <c r="AI28" s="2" t="s">
         <v>564</v>
       </c>
@@ -11587,17 +11639,17 @@
       <c r="G35" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="N35" s="51" t="s">
+      <c r="N35" s="52" t="s">
         <v>636</v>
       </c>
-      <c r="O35" s="51"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="51"/>
-      <c r="R35" s="51"/>
-      <c r="S35" s="51"/>
-      <c r="T35" s="51"/>
-      <c r="U35" s="51"/>
-      <c r="V35" s="51"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="52"/>
+      <c r="V35" s="52"/>
       <c r="W35" s="26"/>
       <c r="X35" s="26"/>
       <c r="Y35" s="26"/>
@@ -11714,10 +11766,10 @@
       </c>
       <c r="X37" s="26"/>
       <c r="Y37" s="26"/>
-      <c r="AC37" s="57" t="s">
+      <c r="AC37" s="53" t="s">
         <v>970</v>
       </c>
-      <c r="AD37" s="57"/>
+      <c r="AD37" s="53"/>
       <c r="AI37" s="2" t="s">
         <v>573</v>
       </c>
@@ -11726,15 +11778,15 @@
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="50"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
       <c r="N38" s="1" t="s">
         <v>640</v>
       </c>
@@ -11764,16 +11816,16 @@
       </c>
       <c r="X38" s="26"/>
       <c r="Y38" s="26"/>
-      <c r="AC38" s="58" t="s">
+      <c r="AC38" s="47" t="s">
         <v>971</v>
       </c>
-      <c r="AD38" s="58" t="s">
+      <c r="AD38" s="47" t="s">
         <v>981</v>
       </c>
-      <c r="AF38" s="49" t="s">
+      <c r="AF38" s="50" t="s">
         <v>631</v>
       </c>
-      <c r="AG38" s="49"/>
+      <c r="AG38" s="50"/>
       <c r="AI38" s="2" t="s">
         <v>574</v>
       </c>
@@ -12038,17 +12090,17 @@
       <c r="I43" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="N43" s="52" t="s">
+      <c r="N43" s="54" t="s">
         <v>982</v>
       </c>
-      <c r="O43" s="52"/>
-      <c r="P43" s="52"/>
-      <c r="Q43" s="52"/>
-      <c r="R43" s="52"/>
-      <c r="S43" s="52"/>
-      <c r="T43" s="52"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="52"/>
+      <c r="O43" s="54"/>
+      <c r="P43" s="54"/>
+      <c r="Q43" s="54"/>
+      <c r="R43" s="54"/>
+      <c r="S43" s="54"/>
+      <c r="T43" s="54"/>
+      <c r="U43" s="54"/>
+      <c r="V43" s="54"/>
       <c r="AI43" s="2" t="s">
         <v>579</v>
       </c>
@@ -12705,11 +12757,9 @@
     <col min="8" max="8" width="26.7109375" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24" style="12" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" style="12"/>
-    <col min="11" max="11" width="9.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="9.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.140625" style="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.42578125" style="12" bestFit="1" customWidth="1"/>
@@ -12733,36 +12783,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
       <c r="L1"/>
-      <c r="O1" s="50" t="s">
+      <c r="O1" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="AC1" s="49" t="s">
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="AC1" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="AD1" s="49"/>
-      <c r="AF1" s="49" t="s">
+      <c r="AD1" s="50"/>
+      <c r="AF1" s="50" t="s">
         <v>393</v>
       </c>
-      <c r="AG1" s="49"/>
-      <c r="AI1" s="49" t="s">
+      <c r="AG1" s="50"/>
+      <c r="AI1" s="50" t="s">
         <v>536</v>
       </c>
-      <c r="AJ1" s="49"/>
+      <c r="AJ1" s="50"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -13040,10 +13090,10 @@
       <c r="AD6" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="AF6" s="49" t="s">
+      <c r="AF6" s="50" t="s">
         <v>413</v>
       </c>
-      <c r="AG6" s="49"/>
+      <c r="AG6" s="50"/>
       <c r="AI6" s="2" t="s">
         <v>542</v>
       </c>
@@ -13315,14 +13365,14 @@
       <c r="T11" s="2">
         <v>8192755945</v>
       </c>
-      <c r="AC11" s="49" t="s">
+      <c r="AC11" s="50" t="s">
         <v>235</v>
       </c>
-      <c r="AD11" s="49"/>
-      <c r="AF11" s="49" t="s">
+      <c r="AD11" s="50"/>
+      <c r="AF11" s="50" t="s">
         <v>414</v>
       </c>
-      <c r="AG11" s="49"/>
+      <c r="AG11" s="50"/>
       <c r="AI11" s="2" t="s">
         <v>547</v>
       </c>
@@ -13410,31 +13460,30 @@
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="K14" s="50" t="s">
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="L14" s="57" t="s">
         <v>386</v>
       </c>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="50"/>
-      <c r="P14" s="50"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50"/>
-      <c r="S14" s="50"/>
-      <c r="T14" s="50"/>
-      <c r="U14" s="50"/>
-      <c r="V14" s="50"/>
-      <c r="W14" s="50"/>
-      <c r="X14" s="50"/>
+      <c r="M14" s="58"/>
+      <c r="N14" s="58"/>
+      <c r="O14" s="58"/>
+      <c r="P14" s="58"/>
+      <c r="Q14" s="58"/>
+      <c r="R14" s="58"/>
+      <c r="S14" s="58"/>
+      <c r="T14" s="58"/>
+      <c r="U14" s="58"/>
+      <c r="V14" s="58"/>
+      <c r="W14" s="58"/>
+      <c r="X14" s="59"/>
       <c r="AC14" s="2" t="s">
         <v>340</v>
       </c>
@@ -13476,20 +13525,17 @@
       <c r="G15" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="L15" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="L15" s="9" t="s">
-        <v>409</v>
-      </c>
       <c r="M15" s="9" t="s">
+        <v>988</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="O15" s="9" t="s">
         <v>654</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>307</v>
       </c>
       <c r="P15" s="9" t="s">
         <v>394</v>
@@ -13553,20 +13599,17 @@
       <c r="G16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>395</v>
@@ -13601,10 +13644,10 @@
       <c r="AD16" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AF16" s="49" t="s">
+      <c r="AF16" s="50" t="s">
         <v>415</v>
       </c>
-      <c r="AG16" s="49"/>
+      <c r="AG16" s="50"/>
       <c r="AI16" s="2" t="s">
         <v>552</v>
       </c>
@@ -13634,20 +13677,17 @@
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>396</v>
@@ -13717,20 +13757,17 @@
       <c r="G18" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>396</v>
@@ -13800,20 +13837,17 @@
       <c r="G19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>396</v>
@@ -13883,20 +13917,17 @@
       <c r="G20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="O20" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>396</v>
@@ -13939,20 +13970,17 @@
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>395</v>
@@ -13987,10 +14015,10 @@
       <c r="AD21" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="AF21" s="49" t="s">
+      <c r="AF21" s="50" t="s">
         <v>431</v>
       </c>
-      <c r="AG21" s="49"/>
+      <c r="AG21" s="50"/>
       <c r="AI21" s="2" t="s">
         <v>557</v>
       </c>
@@ -13999,29 +14027,26 @@
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="K22" s="2" t="s">
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="L22" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>396</v>
@@ -14091,20 +14116,17 @@
       <c r="G23" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="L23" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>395</v>
@@ -14174,20 +14196,17 @@
       <c r="G24" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="L24" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>396</v>
@@ -14257,20 +14276,17 @@
       <c r="G25" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="L25" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>396</v>
@@ -14375,24 +14391,23 @@
       <c r="G27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K27" s="50" t="s">
+      <c r="L27" s="57" t="s">
         <v>410</v>
       </c>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="50"/>
-      <c r="W27" s="50"/>
-      <c r="X27" s="50"/>
-      <c r="Y27" s="50"/>
-      <c r="Z27" s="50"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="58"/>
+      <c r="R27" s="58"/>
+      <c r="S27" s="58"/>
+      <c r="T27" s="58"/>
+      <c r="U27" s="58"/>
+      <c r="V27" s="58"/>
+      <c r="W27" s="58"/>
+      <c r="X27" s="58"/>
+      <c r="Y27" s="58"/>
+      <c r="Z27" s="59"/>
       <c r="AC27" s="2" t="s">
         <v>353</v>
       </c>
@@ -14428,20 +14443,17 @@
       <c r="G28" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="L28" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="M28" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="M28" s="9" t="s">
+      <c r="N28" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="O28" s="9" t="s">
         <v>654</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>307</v>
       </c>
       <c r="P28" s="9" t="s">
         <v>394</v>
@@ -14482,10 +14494,10 @@
       <c r="AD28" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="AG28" s="49"/>
+      <c r="AG28" s="50"/>
       <c r="AI28" s="2" t="s">
         <v>564</v>
       </c>
@@ -14515,20 +14527,17 @@
       <c r="G29" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="L29" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="M29" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="N29" s="7" t="s">
+      <c r="O29" s="7" t="s">
         <v>296</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>396</v>
@@ -14604,20 +14613,17 @@
       <c r="G30" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="L30" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="N30" s="7" t="s">
+      <c r="O30" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>395</v>
@@ -14693,20 +14699,17 @@
       <c r="G31" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="L31" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="N31" s="7" t="s">
+      <c r="O31" s="7" t="s">
         <v>298</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>395</v>
@@ -14782,20 +14785,17 @@
       <c r="G32" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="N32" s="7" t="s">
+      <c r="O32" s="7" t="s">
         <v>299</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>395</v>
@@ -14871,20 +14871,17 @@
       <c r="G33" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="N33" s="7" t="s">
+      <c r="O33" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>395</v>
@@ -14949,10 +14946,10 @@
       <c r="X34" s="25"/>
       <c r="Y34" s="25"/>
       <c r="Z34" s="25"/>
-      <c r="AC34" s="57" t="s">
+      <c r="AC34" s="53" t="s">
         <v>970</v>
       </c>
-      <c r="AD34" s="57"/>
+      <c r="AD34" s="53"/>
       <c r="AF34" s="2" t="s">
         <v>373</v>
       </c>
@@ -14967,33 +14964,33 @@
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
-      <c r="N35" s="51" t="s">
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="N35" s="52" t="s">
         <v>636</v>
       </c>
-      <c r="O35" s="51"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="51"/>
-      <c r="R35" s="51"/>
-      <c r="S35" s="51"/>
-      <c r="T35" s="51"/>
-      <c r="U35" s="51"/>
-      <c r="V35" s="51"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="52"/>
+      <c r="V35" s="52"/>
       <c r="W35" s="26"/>
       <c r="X35" s="26"/>
       <c r="Y35" s="26"/>
-      <c r="AC35" s="58" t="s">
+      <c r="AC35" s="47" t="s">
         <v>971</v>
       </c>
-      <c r="AD35" s="58" t="s">
+      <c r="AD35" s="47" t="s">
         <v>981</v>
       </c>
       <c r="AF35" s="2" t="s">
@@ -15323,10 +15320,10 @@
       <c r="V40" s="14">
         <v>46283.625</v>
       </c>
-      <c r="AF40" s="49" t="s">
+      <c r="AF40" s="50" t="s">
         <v>631</v>
       </c>
-      <c r="AG40" s="49"/>
+      <c r="AG40" s="50"/>
       <c r="AI40" s="2" t="s">
         <v>576</v>
       </c>
@@ -15425,22 +15422,22 @@
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A44" s="55" t="s">
+      <c r="A44" s="60" t="s">
         <v>982</v>
       </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="55"/>
-      <c r="S44" s="56" t="s">
+      <c r="B44" s="60"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="60"/>
+      <c r="S44" s="61" t="s">
         <v>234</v>
       </c>
-      <c r="T44" s="56"/>
-      <c r="U44" s="56"/>
+      <c r="T44" s="61"/>
+      <c r="U44" s="61"/>
       <c r="AI44" s="2" t="s">
         <v>580</v>
       </c>
@@ -17211,14 +17208,13 @@
   <mergeCells count="21">
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="C35:I35"/>
-    <mergeCell ref="K27:Z27"/>
     <mergeCell ref="AF28:AG28"/>
     <mergeCell ref="N35:V35"/>
     <mergeCell ref="AF40:AG40"/>
     <mergeCell ref="S44:U44"/>
     <mergeCell ref="AC34:AD34"/>
+    <mergeCell ref="L27:Z27"/>
     <mergeCell ref="AF21:AG21"/>
-    <mergeCell ref="K14:X14"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="AI1:AJ1"/>
     <mergeCell ref="AF6:AG6"/>
@@ -17230,6 +17226,7 @@
     <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="AF16:AG16"/>
+    <mergeCell ref="L14:X14"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
